--- a/data/location.xlsx
+++ b/data/location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\abhinav_backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EB7894-E54B-4ABA-88FA-CC878D8EFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF617D5-D1F0-45E0-B3C0-F2FF657A58C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6EEA6FC-22B5-452D-A042-C0CBEF8991D7}"/>
   </bookViews>
@@ -1026,8 +1026,8 @@
     <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">

--- a/data/location.xlsx
+++ b/data/location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\abhinav_backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF617D5-D1F0-45E0-B3C0-F2FF657A58C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6B541F-55AA-4E5D-833D-4D4DA0D9F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6EEA6FC-22B5-452D-A042-C0CBEF8991D7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="197">
   <si>
     <t>shop_name</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t>CMP1772169765781</t>
+  </si>
+  <si>
+    <t>Thalakavoor 10.066198 78.723352</t>
   </si>
 </sst>
 </file>
@@ -666,7 +669,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -689,11 +692,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,7 +763,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1016,28 +1092,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE546CBB-9385-4B63-9CAF-DFA6EA3E1E1C}">
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:J306"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="12" customWidth="1"/>
     <col min="3" max="3" width="22.85546875" customWidth="1"/>
     <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="9" t="s">
         <v>193</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1060,13 +1137,13 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1089,13 +1166,13 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1118,13 +1195,13 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1147,13 +1224,13 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1176,13 +1253,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1205,13 +1282,13 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1234,13 +1311,13 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1263,13 +1340,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1292,13 +1369,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1321,13 +1398,13 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1350,13 +1427,13 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1379,13 +1456,13 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1408,13 +1485,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1437,13 +1514,13 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1466,13 +1543,13 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1495,13 +1572,13 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1524,13 +1601,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1553,13 +1630,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1582,13 +1659,13 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="B20" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1611,13 +1688,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B21" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1640,13 +1717,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="B22" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1669,13 +1746,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="B23" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -1698,13 +1775,13 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="B24" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1727,13 +1804,13 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1756,13 +1833,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B26" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1785,13 +1862,13 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="B27" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1814,13 +1891,13 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="B28" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1843,13 +1920,13 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="B29" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1872,13 +1949,13 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="B30" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1901,13 +1978,13 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="B31" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1930,13 +2007,13 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="B32" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1958,14 +2035,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B33" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1987,14 +2064,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="B34" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2016,14 +2093,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C35" s="1" t="s">
+      <c r="B35" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -2045,14 +2122,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B36" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -2074,14 +2151,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="B37" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2103,14 +2180,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="B38" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2132,14 +2209,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="B39" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -2161,14 +2238,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="B40" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -2190,14 +2267,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="B41" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2219,14 +2296,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="B42" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -2248,14 +2325,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2277,14 +2354,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="B44" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2306,14 +2383,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="B45" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2335,14 +2412,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="B46" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2363,15 +2440,18 @@
       <c r="I46" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="J46" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="B47" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2393,14 +2473,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="B48" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2423,13 +2503,13 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="B49" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2452,13 +2532,13 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="B50" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2481,13 +2561,13 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="B51" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2510,13 +2590,13 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="B52" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2539,13 +2619,13 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="B53" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2568,13 +2648,13 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C54" s="1" t="s">
+      <c r="B54" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -2597,13 +2677,13 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="B55" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -2626,13 +2706,13 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="B56" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -2655,13 +2735,13 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C57" s="1" t="s">
+      <c r="B57" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -2684,13 +2764,13 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="B58" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -2713,13 +2793,13 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="B59" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2742,13 +2822,13 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="B60" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -2771,13 +2851,13 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C61" s="1" t="s">
+      <c r="B61" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -2800,13 +2880,13 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C62" s="1" t="s">
+      <c r="B62" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -2829,13 +2909,13 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="B63" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -2858,13 +2938,13 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C64" s="1" t="s">
+      <c r="B64" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -2887,13 +2967,13 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="1" t="s">
+      <c r="B65" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -2916,13 +2996,13 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C66" s="1" t="s">
+      <c r="B66" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -2945,13 +3025,13 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C67" s="1" t="s">
+      <c r="B67" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -2974,13 +3054,13 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C68" s="1" t="s">
+      <c r="B68" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -3003,13 +3083,13 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C69" s="1" t="s">
+      <c r="B69" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3032,13 +3112,13 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C70" s="1" t="s">
+      <c r="B70" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C70" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3061,13 +3141,13 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C71" s="1" t="s">
+      <c r="B71" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3090,13 +3170,13 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="B72" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3119,13 +3199,13 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C73" s="1" t="s">
+      <c r="B73" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3148,13 +3228,13 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="B74" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -3177,13 +3257,13 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C75" s="1" t="s">
+      <c r="B75" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3206,13 +3286,13 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C76" s="1" t="s">
+      <c r="B76" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -3235,13 +3315,13 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C77" s="1" t="s">
+      <c r="B77" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -3264,13 +3344,13 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C78" s="1" t="s">
+      <c r="B78" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3293,13 +3373,13 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C79" s="1" t="s">
+      <c r="B79" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D79" s="3"/>
@@ -3314,13 +3394,13 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C80" s="1" t="s">
+      <c r="B80" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3343,13 +3423,13 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C81" s="1" t="s">
+      <c r="B81" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3372,13 +3452,13 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C82" s="1" t="s">
+      <c r="B82" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3401,13 +3481,13 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C83" s="1" t="s">
+      <c r="B83" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3430,13 +3510,13 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C84" s="1" t="s">
+      <c r="B84" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3459,13 +3539,13 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C85" s="1" t="s">
+      <c r="B85" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3488,13 +3568,13 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="B86" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3517,13 +3597,13 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C87" s="1" t="s">
+      <c r="B87" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3546,13 +3626,13 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="1" t="s">
+      <c r="B88" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3575,13 +3655,13 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C89" s="1" t="s">
+      <c r="B89" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3604,13 +3684,13 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="B90" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3633,13 +3713,13 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C91" s="1" t="s">
+      <c r="B91" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3662,11 +3742,13 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C92" s="1" t="s">
+      <c r="A92" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D92" s="1"/>
@@ -3679,11 +3761,11 @@
       <c r="I92" s="1"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C93" s="1" t="s">
+      <c r="A93" s="7"/>
+      <c r="B93" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D93" s="1"/>
@@ -3696,11 +3778,11 @@
       <c r="I93" s="1"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C94" s="1" t="s">
+      <c r="A94" s="14"/>
+      <c r="B94" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C94" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D94" s="1"/>
@@ -3714,10 +3796,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C95" s="1" t="s">
+      <c r="B95" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C95" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D95" s="1"/>
@@ -3731,10 +3813,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C96" s="1" t="s">
+      <c r="B96" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C96" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D96" s="1"/>
@@ -3748,10 +3830,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C97" s="1" t="s">
+      <c r="B97" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D97" s="1"/>
@@ -3765,10 +3847,10 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C98" s="1" t="s">
+      <c r="B98" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D98" s="1"/>
@@ -3782,10 +3864,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="1" t="s">
+      <c r="B99" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D99" s="1"/>
@@ -3799,10 +3881,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
-      <c r="B100" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C100" s="1" t="s">
+      <c r="B100" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D100" s="1"/>
@@ -3816,10 +3898,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
-      <c r="B101" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C101" s="1" t="s">
+      <c r="B101" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C101" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D101" s="1"/>
@@ -3832,11 +3914,11 @@
       <c r="I101" s="1"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="B102" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C102" s="1" t="s">
+      <c r="A102" s="15"/>
+      <c r="B102" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D102" s="1"/>
@@ -3849,11 +3931,11 @@
       <c r="I102" s="1"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="B103" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C103" s="1" t="s">
+      <c r="A103" s="7"/>
+      <c r="B103" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C103" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D103" s="1"/>
@@ -3866,11 +3948,11 @@
       <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C104" s="1" t="s">
+      <c r="A104" s="7"/>
+      <c r="B104" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C104" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D104" s="1"/>
@@ -3883,11 +3965,11 @@
       <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C105" s="1" t="s">
+      <c r="A105" s="7"/>
+      <c r="B105" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C105" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D105" s="1"/>
@@ -3900,11 +3982,11 @@
       <c r="I105" s="1"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="B106" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C106" s="1" t="s">
+      <c r="A106" s="7"/>
+      <c r="B106" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D106" s="1"/>
@@ -3917,11 +3999,11 @@
       <c r="I106" s="1"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C107" s="1" t="s">
+      <c r="A107" s="7"/>
+      <c r="B107" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D107" s="1"/>
@@ -3934,11 +4016,11 @@
       <c r="I107" s="1"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C108" s="1" t="s">
+      <c r="A108" s="7"/>
+      <c r="B108" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D108" s="1"/>
@@ -3951,11 +4033,11 @@
       <c r="I108" s="1"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C109" s="1" t="s">
+      <c r="A109" s="7"/>
+      <c r="B109" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D109" s="1"/>
@@ -3968,11 +4050,11 @@
       <c r="I109" s="1"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="B110" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C110" s="1" t="s">
+      <c r="A110" s="7"/>
+      <c r="B110" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D110" s="1"/>
@@ -3985,9 +4067,9 @@
       <c r="I110" s="1"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
+      <c r="A111" s="7"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
+      <c r="C111" s="10"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -3998,9 +4080,9 @@
       <c r="I111" s="1"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
+      <c r="A112" s="7"/>
       <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+      <c r="C112" s="10"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4011,9 +4093,9 @@
       <c r="I112" s="1"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
+      <c r="A113" s="7"/>
       <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
+      <c r="C113" s="10"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4024,9 +4106,9 @@
       <c r="I113" s="1"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
+      <c r="A114" s="7"/>
       <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
+      <c r="C114" s="10"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -4037,9 +4119,9 @@
       <c r="I114" s="1"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
+      <c r="A115" s="7"/>
       <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
+      <c r="C115" s="10"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
@@ -4050,9 +4132,9 @@
       <c r="I115" s="1"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
+      <c r="A116" s="7"/>
       <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
+      <c r="C116" s="10"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -4063,9 +4145,9 @@
       <c r="I116" s="1"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
+      <c r="A117" s="7"/>
       <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
+      <c r="C117" s="10"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -4076,9 +4158,9 @@
       <c r="I117" s="1"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
+      <c r="A118" s="7"/>
       <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
+      <c r="C118" s="10"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -4089,9 +4171,9 @@
       <c r="I118" s="1"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
+      <c r="A119" s="7"/>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+      <c r="C119" s="10"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -4102,9 +4184,9 @@
       <c r="I119" s="1"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
+      <c r="A120" s="7"/>
       <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
+      <c r="C120" s="10"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -4115,9 +4197,9 @@
       <c r="I120" s="1"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
+      <c r="A121" s="7"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
+      <c r="C121" s="10"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -4128,9 +4210,9 @@
       <c r="I121" s="1"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
+      <c r="A122" s="7"/>
       <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
+      <c r="C122" s="10"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -4141,9 +4223,9 @@
       <c r="I122" s="1"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
+      <c r="A123" s="7"/>
       <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
+      <c r="C123" s="10"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -4154,9 +4236,9 @@
       <c r="I123" s="1"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
+      <c r="A124" s="7"/>
       <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
+      <c r="C124" s="10"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -4167,9 +4249,9 @@
       <c r="I124" s="1"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
+      <c r="A125" s="7"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
+      <c r="C125" s="10"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -4180,9 +4262,9 @@
       <c r="I125" s="1"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
+      <c r="A126" s="7"/>
       <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
+      <c r="C126" s="10"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -4193,9 +4275,9 @@
       <c r="I126" s="1"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
+      <c r="A127" s="7"/>
       <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
+      <c r="C127" s="10"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -4206,9 +4288,9 @@
       <c r="I127" s="1"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
+      <c r="A128" s="7"/>
       <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
+      <c r="C128" s="10"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4219,9 +4301,9 @@
       <c r="I128" s="1"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
+      <c r="A129" s="7"/>
       <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
+      <c r="C129" s="10"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4232,9 +4314,9 @@
       <c r="I129" s="1"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
+      <c r="A130" s="7"/>
       <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
+      <c r="C130" s="10"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -4245,9 +4327,9 @@
       <c r="I130" s="1"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
+      <c r="A131" s="7"/>
       <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
+      <c r="C131" s="10"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4258,9 +4340,9 @@
       <c r="I131" s="1"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
+      <c r="A132" s="7"/>
       <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
+      <c r="C132" s="10"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -4269,9 +4351,9 @@
       <c r="I132" s="1"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
+      <c r="A133" s="7"/>
       <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
+      <c r="C133" s="10"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -4280,9 +4362,9 @@
       <c r="I133" s="1"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
+      <c r="A134" s="7"/>
       <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
+      <c r="C134" s="10"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -4291,9 +4373,9 @@
       <c r="I134" s="1"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
+      <c r="A135" s="7"/>
       <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
+      <c r="C135" s="10"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
@@ -4302,9 +4384,9 @@
       <c r="I135" s="1"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="1"/>
+      <c r="A136" s="7"/>
       <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
+      <c r="C136" s="10"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -4313,9 +4395,9 @@
       <c r="I136" s="1"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="1"/>
+      <c r="A137" s="7"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
+      <c r="C137" s="10"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -4324,9 +4406,9 @@
       <c r="I137" s="1"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="1"/>
+      <c r="A138" s="7"/>
       <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
+      <c r="C138" s="10"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -4335,9 +4417,9 @@
       <c r="I138" s="1"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
+      <c r="A139" s="7"/>
       <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
+      <c r="C139" s="10"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -4346,9 +4428,9 @@
       <c r="I139" s="1"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
+      <c r="A140" s="7"/>
       <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
+      <c r="C140" s="10"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -4357,9 +4439,9 @@
       <c r="I140" s="1"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="1"/>
+      <c r="A141" s="7"/>
       <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
+      <c r="C141" s="10"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -4368,9 +4450,9 @@
       <c r="I141" s="1"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="1"/>
+      <c r="A142" s="7"/>
       <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
+      <c r="C142" s="10"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -4379,9 +4461,9 @@
       <c r="I142" s="1"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="1"/>
+      <c r="A143" s="7"/>
       <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
+      <c r="C143" s="10"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -4390,9 +4472,9 @@
       <c r="I143" s="1"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="1"/>
+      <c r="A144" s="7"/>
       <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
+      <c r="C144" s="10"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
@@ -4401,9 +4483,9 @@
       <c r="I144" s="1"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="1"/>
+      <c r="A145" s="7"/>
       <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
+      <c r="C145" s="10"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -4412,9 +4494,9 @@
       <c r="I145" s="1"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="1"/>
+      <c r="A146" s="7"/>
       <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
+      <c r="C146" s="10"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -4423,9 +4505,9 @@
       <c r="I146" s="1"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="1"/>
+      <c r="A147" s="7"/>
       <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
+      <c r="C147" s="10"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -4434,9 +4516,9 @@
       <c r="I147" s="1"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="1"/>
+      <c r="A148" s="7"/>
       <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
+      <c r="C148" s="10"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -4445,9 +4527,9 @@
       <c r="I148" s="1"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="1"/>
+      <c r="A149" s="7"/>
       <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
+      <c r="C149" s="10"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -4456,9 +4538,9 @@
       <c r="I149" s="1"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="1"/>
+      <c r="A150" s="7"/>
       <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
+      <c r="C150" s="10"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -4467,9 +4549,9 @@
       <c r="I150" s="1"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="1"/>
+      <c r="A151" s="7"/>
       <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
+      <c r="C151" s="10"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -4478,9 +4560,9 @@
       <c r="I151" s="1"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
+      <c r="A152" s="7"/>
       <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
+      <c r="C152" s="10"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
@@ -4489,9 +4571,9 @@
       <c r="I152" s="1"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
+      <c r="A153" s="7"/>
       <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
+      <c r="C153" s="10"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -4500,9 +4582,9 @@
       <c r="I153" s="1"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
+      <c r="A154" s="7"/>
       <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
+      <c r="C154" s="10"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -4511,9 +4593,9 @@
       <c r="I154" s="1"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
+      <c r="A155" s="7"/>
       <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
+      <c r="C155" s="10"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -4522,9 +4604,9 @@
       <c r="I155" s="1"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="1"/>
+      <c r="A156" s="7"/>
       <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
+      <c r="C156" s="10"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
@@ -4533,9 +4615,9 @@
       <c r="I156" s="1"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
+      <c r="A157" s="7"/>
       <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
+      <c r="C157" s="10"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -4544,9 +4626,9 @@
       <c r="I157" s="1"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
+      <c r="A158" s="7"/>
       <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
+      <c r="C158" s="10"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
@@ -4555,9 +4637,9 @@
       <c r="I158" s="1"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="1"/>
+      <c r="A159" s="7"/>
       <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
+      <c r="C159" s="10"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -4566,9 +4648,9 @@
       <c r="I159" s="1"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
+      <c r="A160" s="7"/>
       <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
+      <c r="C160" s="10"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -4577,9 +4659,9 @@
       <c r="I160" s="1"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
+      <c r="A161" s="7"/>
       <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
+      <c r="C161" s="10"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
@@ -4588,9 +4670,9 @@
       <c r="I161" s="1"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
+      <c r="A162" s="7"/>
       <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
+      <c r="C162" s="10"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -4599,9 +4681,9 @@
       <c r="I162" s="1"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="1"/>
+      <c r="A163" s="7"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
+      <c r="C163" s="10"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -4610,9 +4692,9 @@
       <c r="I163" s="1"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="1"/>
+      <c r="A164" s="7"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
+      <c r="C164" s="10"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
@@ -4621,9 +4703,9 @@
       <c r="I164" s="1"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="1"/>
+      <c r="A165" s="7"/>
       <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
+      <c r="C165" s="10"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -4632,9 +4714,9 @@
       <c r="I165" s="1"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="1"/>
+      <c r="A166" s="7"/>
       <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
+      <c r="C166" s="10"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
@@ -4643,9 +4725,9 @@
       <c r="I166" s="1"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="1"/>
+      <c r="A167" s="7"/>
       <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
+      <c r="C167" s="10"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
@@ -4654,9 +4736,9 @@
       <c r="I167" s="1"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="1"/>
+      <c r="A168" s="7"/>
       <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
+      <c r="C168" s="10"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
@@ -4665,9 +4747,9 @@
       <c r="I168" s="1"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="1"/>
+      <c r="A169" s="7"/>
       <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
+      <c r="C169" s="10"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
@@ -4676,9 +4758,9 @@
       <c r="I169" s="1"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="1"/>
+      <c r="A170" s="7"/>
       <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
+      <c r="C170" s="10"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
@@ -4687,9 +4769,9 @@
       <c r="I170" s="1"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="1"/>
+      <c r="A171" s="7"/>
       <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
+      <c r="C171" s="10"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -4698,9 +4780,9 @@
       <c r="I171" s="1"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="1"/>
+      <c r="A172" s="7"/>
       <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
+      <c r="C172" s="10"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -4709,9 +4791,9 @@
       <c r="I172" s="1"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="1"/>
+      <c r="A173" s="7"/>
       <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
+      <c r="C173" s="10"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
@@ -4720,9 +4802,9 @@
       <c r="I173" s="1"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="1"/>
+      <c r="A174" s="7"/>
       <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
+      <c r="C174" s="10"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -4731,9 +4813,9 @@
       <c r="I174" s="1"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
+      <c r="A175" s="7"/>
       <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
+      <c r="C175" s="10"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -4742,9 +4824,9 @@
       <c r="I175" s="1"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="1"/>
+      <c r="A176" s="7"/>
       <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
+      <c r="C176" s="10"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
@@ -4753,9 +4835,9 @@
       <c r="I176" s="1"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="1"/>
+      <c r="A177" s="7"/>
       <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
+      <c r="C177" s="10"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
@@ -4764,9 +4846,9 @@
       <c r="I177" s="1"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="1"/>
+      <c r="A178" s="7"/>
       <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
+      <c r="C178" s="10"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
@@ -4775,9 +4857,9 @@
       <c r="I178" s="1"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="1"/>
+      <c r="A179" s="7"/>
       <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
+      <c r="C179" s="10"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
@@ -4786,9 +4868,9 @@
       <c r="I179" s="1"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="1"/>
+      <c r="A180" s="7"/>
       <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
+      <c r="C180" s="10"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
@@ -4797,9 +4879,9 @@
       <c r="I180" s="1"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="1"/>
+      <c r="A181" s="7"/>
       <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
+      <c r="C181" s="10"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
@@ -4808,9 +4890,9 @@
       <c r="I181" s="1"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="1"/>
+      <c r="A182" s="7"/>
       <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
+      <c r="C182" s="10"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -4819,9 +4901,9 @@
       <c r="I182" s="1"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="1"/>
+      <c r="A183" s="7"/>
       <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
+      <c r="C183" s="10"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -4830,9 +4912,9 @@
       <c r="I183" s="1"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="1"/>
+      <c r="A184" s="7"/>
       <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
+      <c r="C184" s="10"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
@@ -4841,9 +4923,9 @@
       <c r="I184" s="1"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="1"/>
+      <c r="A185" s="7"/>
       <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
+      <c r="C185" s="10"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -4852,9 +4934,9 @@
       <c r="I185" s="1"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="1"/>
+      <c r="A186" s="7"/>
       <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
+      <c r="C186" s="10"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -4863,9 +4945,9 @@
       <c r="I186" s="1"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="1"/>
+      <c r="A187" s="7"/>
       <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
+      <c r="C187" s="10"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
@@ -4874,9 +4956,9 @@
       <c r="I187" s="1"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="1"/>
+      <c r="A188" s="7"/>
       <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
+      <c r="C188" s="10"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
@@ -4885,9 +4967,9 @@
       <c r="I188" s="1"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="1"/>
+      <c r="A189" s="7"/>
       <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
+      <c r="C189" s="10"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -4896,9 +4978,9 @@
       <c r="I189" s="1"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="1"/>
+      <c r="A190" s="7"/>
       <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
+      <c r="C190" s="10"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -4907,9 +4989,9 @@
       <c r="I190" s="1"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="1"/>
+      <c r="A191" s="7"/>
       <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
+      <c r="C191" s="10"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
@@ -4918,9 +5000,9 @@
       <c r="I191" s="1"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="1"/>
+      <c r="A192" s="7"/>
       <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
+      <c r="C192" s="10"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
@@ -4929,9 +5011,9 @@
       <c r="I192" s="1"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="1"/>
+      <c r="A193" s="7"/>
       <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
+      <c r="C193" s="10"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -4940,9 +5022,9 @@
       <c r="I193" s="1"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="1"/>
+      <c r="A194" s="7"/>
       <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
+      <c r="C194" s="10"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
@@ -4951,9 +5033,9 @@
       <c r="I194" s="1"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="1"/>
+      <c r="A195" s="7"/>
       <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
+      <c r="C195" s="10"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -4962,9 +5044,9 @@
       <c r="I195" s="1"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="1"/>
+      <c r="A196" s="7"/>
       <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
+      <c r="C196" s="10"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
@@ -4973,9 +5055,9 @@
       <c r="I196" s="1"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="1"/>
+      <c r="A197" s="7"/>
       <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
+      <c r="C197" s="10"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -4984,9 +5066,9 @@
       <c r="I197" s="1"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="1"/>
+      <c r="A198" s="7"/>
       <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
+      <c r="C198" s="10"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -4995,9 +5077,9 @@
       <c r="I198" s="1"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="1"/>
+      <c r="A199" s="7"/>
       <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
+      <c r="C199" s="10"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
@@ -5006,9 +5088,9 @@
       <c r="I199" s="1"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="1"/>
+      <c r="A200" s="7"/>
       <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
+      <c r="C200" s="10"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
@@ -5017,9 +5099,9 @@
       <c r="I200" s="1"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="1"/>
+      <c r="A201" s="7"/>
       <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
+      <c r="C201" s="10"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -5028,9 +5110,9 @@
       <c r="I201" s="1"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="1"/>
+      <c r="A202" s="7"/>
       <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
+      <c r="C202" s="10"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -5039,9 +5121,9 @@
       <c r="I202" s="1"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="1"/>
+      <c r="A203" s="7"/>
       <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
+      <c r="C203" s="10"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
@@ -5050,9 +5132,9 @@
       <c r="I203" s="1"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="1"/>
+      <c r="A204" s="7"/>
       <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
+      <c r="C204" s="10"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -5061,9 +5143,9 @@
       <c r="I204" s="1"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="1"/>
+      <c r="A205" s="7"/>
       <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
+      <c r="C205" s="10"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
@@ -5072,9 +5154,9 @@
       <c r="I205" s="1"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="1"/>
+      <c r="A206" s="7"/>
       <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
+      <c r="C206" s="10"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -5083,9 +5165,9 @@
       <c r="I206" s="1"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="1"/>
+      <c r="A207" s="7"/>
       <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
+      <c r="C207" s="10"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
@@ -5094,9 +5176,9 @@
       <c r="I207" s="1"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="1"/>
+      <c r="A208" s="7"/>
       <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
+      <c r="C208" s="10"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
@@ -5105,9 +5187,9 @@
       <c r="I208" s="1"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="1"/>
+      <c r="A209" s="7"/>
       <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
+      <c r="C209" s="10"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -5116,9 +5198,9 @@
       <c r="I209" s="1"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="1"/>
+      <c r="A210" s="7"/>
       <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
+      <c r="C210" s="10"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -5127,9 +5209,9 @@
       <c r="I210" s="1"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="1"/>
+      <c r="A211" s="7"/>
       <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
+      <c r="C211" s="10"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -5138,9 +5220,9 @@
       <c r="I211" s="1"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="1"/>
+      <c r="A212" s="7"/>
       <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
+      <c r="C212" s="10"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
@@ -5149,9 +5231,9 @@
       <c r="I212" s="1"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="1"/>
+      <c r="A213" s="7"/>
       <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
+      <c r="C213" s="10"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -5160,9 +5242,9 @@
       <c r="I213" s="1"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="1"/>
+      <c r="A214" s="7"/>
       <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
+      <c r="C214" s="10"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
@@ -5171,9 +5253,9 @@
       <c r="I214" s="1"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="1"/>
+      <c r="A215" s="7"/>
       <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
+      <c r="C215" s="10"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
@@ -5182,9 +5264,9 @@
       <c r="I215" s="1"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="1"/>
+      <c r="A216" s="7"/>
       <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
+      <c r="C216" s="10"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
@@ -5193,9 +5275,9 @@
       <c r="I216" s="1"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="1"/>
+      <c r="A217" s="7"/>
       <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
+      <c r="C217" s="10"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
@@ -5204,9 +5286,9 @@
       <c r="I217" s="1"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="1"/>
+      <c r="A218" s="7"/>
       <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
+      <c r="C218" s="10"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
@@ -5215,9 +5297,9 @@
       <c r="I218" s="1"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="1"/>
+      <c r="A219" s="7"/>
       <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
+      <c r="C219" s="10"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
@@ -5226,9 +5308,9 @@
       <c r="I219" s="1"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="1"/>
+      <c r="A220" s="7"/>
       <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
+      <c r="C220" s="10"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
@@ -5237,9 +5319,9 @@
       <c r="I220" s="1"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="1"/>
+      <c r="A221" s="7"/>
       <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
+      <c r="C221" s="10"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
@@ -5248,9 +5330,9 @@
       <c r="I221" s="1"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A222" s="1"/>
+      <c r="A222" s="7"/>
       <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
+      <c r="C222" s="10"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -5259,9 +5341,9 @@
       <c r="I222" s="1"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="1"/>
+      <c r="A223" s="7"/>
       <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
+      <c r="C223" s="10"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
@@ -5270,9 +5352,9 @@
       <c r="I223" s="1"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" s="1"/>
+      <c r="A224" s="7"/>
       <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
+      <c r="C224" s="10"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
@@ -5281,9 +5363,9 @@
       <c r="I224" s="1"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="1"/>
+      <c r="A225" s="7"/>
       <c r="B225" s="1"/>
-      <c r="C225" s="1"/>
+      <c r="C225" s="10"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
@@ -5292,9 +5374,9 @@
       <c r="I225" s="1"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="1"/>
+      <c r="A226" s="7"/>
       <c r="B226" s="1"/>
-      <c r="C226" s="1"/>
+      <c r="C226" s="10"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -5303,9 +5385,9 @@
       <c r="I226" s="1"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="1"/>
+      <c r="A227" s="7"/>
       <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
+      <c r="C227" s="10"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -5314,9 +5396,9 @@
       <c r="I227" s="1"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="1"/>
+      <c r="A228" s="7"/>
       <c r="B228" s="1"/>
-      <c r="C228" s="1"/>
+      <c r="C228" s="10"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
@@ -5325,9 +5407,9 @@
       <c r="I228" s="1"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="1"/>
+      <c r="A229" s="7"/>
       <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
+      <c r="C229" s="10"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
@@ -5336,9 +5418,9 @@
       <c r="I229" s="1"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="1"/>
+      <c r="A230" s="7"/>
       <c r="B230" s="1"/>
-      <c r="C230" s="1"/>
+      <c r="C230" s="10"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
@@ -5347,9 +5429,9 @@
       <c r="I230" s="1"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="1"/>
+      <c r="A231" s="7"/>
       <c r="B231" s="1"/>
-      <c r="C231" s="1"/>
+      <c r="C231" s="10"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
@@ -5358,9 +5440,9 @@
       <c r="I231" s="1"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A232" s="1"/>
+      <c r="A232" s="7"/>
       <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
+      <c r="C232" s="10"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
@@ -5369,9 +5451,9 @@
       <c r="I232" s="1"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A233" s="1"/>
+      <c r="A233" s="7"/>
       <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
+      <c r="C233" s="10"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
@@ -5380,9 +5462,9 @@
       <c r="I233" s="1"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A234" s="1"/>
+      <c r="A234" s="7"/>
       <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
+      <c r="C234" s="10"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
@@ -5391,9 +5473,9 @@
       <c r="I234" s="1"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="1"/>
+      <c r="A235" s="7"/>
       <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
+      <c r="C235" s="10"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
@@ -5402,9 +5484,9 @@
       <c r="I235" s="1"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A236" s="1"/>
+      <c r="A236" s="7"/>
       <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
+      <c r="C236" s="10"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
@@ -5413,9 +5495,9 @@
       <c r="I236" s="1"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="1"/>
+      <c r="A237" s="7"/>
       <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
+      <c r="C237" s="10"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
@@ -5424,9 +5506,9 @@
       <c r="I237" s="1"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="1"/>
+      <c r="A238" s="7"/>
       <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
+      <c r="C238" s="10"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
@@ -5435,9 +5517,9 @@
       <c r="I238" s="1"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A239" s="1"/>
+      <c r="A239" s="7"/>
       <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
+      <c r="C239" s="10"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
@@ -5446,9 +5528,9 @@
       <c r="I239" s="1"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A240" s="1"/>
+      <c r="A240" s="7"/>
       <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
+      <c r="C240" s="10"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -5457,9 +5539,9 @@
       <c r="I240" s="1"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A241" s="1"/>
+      <c r="A241" s="7"/>
       <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
+      <c r="C241" s="10"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -5468,9 +5550,9 @@
       <c r="I241" s="1"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="1"/>
+      <c r="A242" s="7"/>
       <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
+      <c r="C242" s="10"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -5479,9 +5561,9 @@
       <c r="I242" s="1"/>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A243" s="1"/>
+      <c r="A243" s="7"/>
       <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
+      <c r="C243" s="10"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -5490,9 +5572,9 @@
       <c r="I243" s="1"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A244" s="1"/>
+      <c r="A244" s="7"/>
       <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
+      <c r="C244" s="10"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -5501,9 +5583,9 @@
       <c r="I244" s="1"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A245" s="1"/>
+      <c r="A245" s="7"/>
       <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
+      <c r="C245" s="10"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -5512,9 +5594,9 @@
       <c r="I245" s="1"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A246" s="1"/>
+      <c r="A246" s="7"/>
       <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
+      <c r="C246" s="10"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -5523,9 +5605,9 @@
       <c r="I246" s="1"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A247" s="1"/>
+      <c r="A247" s="7"/>
       <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
+      <c r="C247" s="10"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -5534,9 +5616,9 @@
       <c r="I247" s="1"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A248" s="1"/>
+      <c r="A248" s="7"/>
       <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
+      <c r="C248" s="10"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -5545,9 +5627,9 @@
       <c r="I248" s="1"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A249" s="1"/>
+      <c r="A249" s="7"/>
       <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
+      <c r="C249" s="10"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -5556,9 +5638,9 @@
       <c r="I249" s="1"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A250" s="1"/>
+      <c r="A250" s="7"/>
       <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
+      <c r="C250" s="10"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -5567,9 +5649,9 @@
       <c r="I250" s="1"/>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A251" s="1"/>
+      <c r="A251" s="7"/>
       <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
+      <c r="C251" s="10"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -5578,9 +5660,9 @@
       <c r="I251" s="1"/>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A252" s="1"/>
+      <c r="A252" s="7"/>
       <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
+      <c r="C252" s="10"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -5589,9 +5671,9 @@
       <c r="I252" s="1"/>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A253" s="1"/>
+      <c r="A253" s="7"/>
       <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
+      <c r="C253" s="10"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
@@ -5600,9 +5682,9 @@
       <c r="I253" s="1"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A254" s="1"/>
+      <c r="A254" s="7"/>
       <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
+      <c r="C254" s="10"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
@@ -5611,9 +5693,9 @@
       <c r="I254" s="1"/>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A255" s="1"/>
+      <c r="A255" s="7"/>
       <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
+      <c r="C255" s="10"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
@@ -5622,9 +5704,9 @@
       <c r="I255" s="1"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A256" s="1"/>
+      <c r="A256" s="7"/>
       <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
+      <c r="C256" s="10"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
@@ -5633,9 +5715,9 @@
       <c r="I256" s="1"/>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A257" s="1"/>
+      <c r="A257" s="7"/>
       <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
+      <c r="C257" s="10"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -5644,9 +5726,9 @@
       <c r="I257" s="1"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A258" s="1"/>
+      <c r="A258" s="7"/>
       <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
+      <c r="C258" s="10"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -5655,9 +5737,9 @@
       <c r="I258" s="1"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A259" s="1"/>
+      <c r="A259" s="7"/>
       <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
+      <c r="C259" s="10"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
@@ -5666,9 +5748,9 @@
       <c r="I259" s="1"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A260" s="1"/>
+      <c r="A260" s="7"/>
       <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
+      <c r="C260" s="10"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
@@ -5677,9 +5759,9 @@
       <c r="I260" s="1"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A261" s="1"/>
+      <c r="A261" s="7"/>
       <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
+      <c r="C261" s="10"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
@@ -5688,9 +5770,9 @@
       <c r="I261" s="1"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A262" s="1"/>
+      <c r="A262" s="7"/>
       <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
+      <c r="C262" s="10"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
@@ -5699,9 +5781,9 @@
       <c r="I262" s="1"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A263" s="1"/>
+      <c r="A263" s="7"/>
       <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
+      <c r="C263" s="10"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -5710,9 +5792,9 @@
       <c r="I263" s="1"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A264" s="1"/>
+      <c r="A264" s="7"/>
       <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
+      <c r="C264" s="10"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
@@ -5721,9 +5803,9 @@
       <c r="I264" s="1"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A265" s="1"/>
+      <c r="A265" s="7"/>
       <c r="B265" s="1"/>
-      <c r="C265" s="1"/>
+      <c r="C265" s="10"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
@@ -5732,9 +5814,9 @@
       <c r="I265" s="1"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A266" s="1"/>
+      <c r="A266" s="7"/>
       <c r="B266" s="1"/>
-      <c r="C266" s="1"/>
+      <c r="C266" s="10"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
@@ -5743,9 +5825,9 @@
       <c r="I266" s="1"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A267" s="1"/>
+      <c r="A267" s="7"/>
       <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
+      <c r="C267" s="10"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
@@ -5754,9 +5836,9 @@
       <c r="I267" s="1"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A268" s="1"/>
+      <c r="A268" s="7"/>
       <c r="B268" s="1"/>
-      <c r="C268" s="1"/>
+      <c r="C268" s="10"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
@@ -5765,9 +5847,9 @@
       <c r="I268" s="1"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A269" s="1"/>
+      <c r="A269" s="7"/>
       <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
+      <c r="C269" s="10"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
@@ -5776,9 +5858,9 @@
       <c r="I269" s="1"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A270" s="1"/>
+      <c r="A270" s="7"/>
       <c r="B270" s="1"/>
-      <c r="C270" s="1"/>
+      <c r="C270" s="10"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
@@ -5787,9 +5869,9 @@
       <c r="I270" s="1"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A271" s="1"/>
+      <c r="A271" s="7"/>
       <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
+      <c r="C271" s="10"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
@@ -5798,9 +5880,9 @@
       <c r="I271" s="1"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A272" s="1"/>
+      <c r="A272" s="7"/>
       <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
+      <c r="C272" s="10"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
@@ -5809,9 +5891,9 @@
       <c r="I272" s="1"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A273" s="1"/>
+      <c r="A273" s="7"/>
       <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
+      <c r="C273" s="10"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
@@ -5820,9 +5902,9 @@
       <c r="I273" s="1"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A274" s="1"/>
+      <c r="A274" s="7"/>
       <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
+      <c r="C274" s="10"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
@@ -5831,9 +5913,9 @@
       <c r="I274" s="1"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A275" s="1"/>
+      <c r="A275" s="7"/>
       <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
+      <c r="C275" s="10"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
@@ -5842,9 +5924,9 @@
       <c r="I275" s="1"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A276" s="1"/>
+      <c r="A276" s="7"/>
       <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
+      <c r="C276" s="10"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
@@ -5853,9 +5935,9 @@
       <c r="I276" s="1"/>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A277" s="1"/>
+      <c r="A277" s="7"/>
       <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
+      <c r="C277" s="10"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
@@ -5864,9 +5946,9 @@
       <c r="I277" s="1"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A278" s="1"/>
+      <c r="A278" s="7"/>
       <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
+      <c r="C278" s="10"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
@@ -5875,9 +5957,9 @@
       <c r="I278" s="1"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A279" s="1"/>
+      <c r="A279" s="7"/>
       <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
+      <c r="C279" s="10"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
@@ -5886,9 +5968,9 @@
       <c r="I279" s="1"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A280" s="1"/>
+      <c r="A280" s="7"/>
       <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
+      <c r="C280" s="10"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
@@ -5897,9 +5979,9 @@
       <c r="I280" s="1"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A281" s="1"/>
+      <c r="A281" s="7"/>
       <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
+      <c r="C281" s="10"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
@@ -5908,9 +5990,9 @@
       <c r="I281" s="1"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A282" s="1"/>
+      <c r="A282" s="7"/>
       <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
+      <c r="C282" s="10"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
@@ -5919,9 +6001,9 @@
       <c r="I282" s="1"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A283" s="1"/>
+      <c r="A283" s="7"/>
       <c r="B283" s="1"/>
-      <c r="C283" s="1"/>
+      <c r="C283" s="10"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
@@ -5930,9 +6012,9 @@
       <c r="I283" s="1"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A284" s="1"/>
+      <c r="A284" s="7"/>
       <c r="B284" s="1"/>
-      <c r="C284" s="1"/>
+      <c r="C284" s="10"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
@@ -5941,9 +6023,9 @@
       <c r="I284" s="1"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A285" s="1"/>
+      <c r="A285" s="7"/>
       <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
+      <c r="C285" s="10"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
@@ -5952,9 +6034,9 @@
       <c r="I285" s="1"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A286" s="1"/>
+      <c r="A286" s="7"/>
       <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
+      <c r="C286" s="10"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
@@ -5963,9 +6045,9 @@
       <c r="I286" s="1"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A287" s="1"/>
+      <c r="A287" s="7"/>
       <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
+      <c r="C287" s="10"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
@@ -5974,9 +6056,9 @@
       <c r="I287" s="1"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A288" s="1"/>
+      <c r="A288" s="7"/>
       <c r="B288" s="1"/>
-      <c r="C288" s="1"/>
+      <c r="C288" s="10"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
@@ -5985,9 +6067,9 @@
       <c r="I288" s="1"/>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A289" s="1"/>
+      <c r="A289" s="7"/>
       <c r="B289" s="1"/>
-      <c r="C289" s="1"/>
+      <c r="C289" s="10"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
@@ -5996,9 +6078,9 @@
       <c r="I289" s="1"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A290" s="1"/>
+      <c r="A290" s="7"/>
       <c r="B290" s="1"/>
-      <c r="C290" s="1"/>
+      <c r="C290" s="10"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
@@ -6007,9 +6089,9 @@
       <c r="I290" s="1"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A291" s="1"/>
+      <c r="A291" s="7"/>
       <c r="B291" s="1"/>
-      <c r="C291" s="1"/>
+      <c r="C291" s="10"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
@@ -6018,9 +6100,9 @@
       <c r="I291" s="1"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A292" s="1"/>
+      <c r="A292" s="7"/>
       <c r="B292" s="1"/>
-      <c r="C292" s="1"/>
+      <c r="C292" s="10"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
@@ -6029,9 +6111,9 @@
       <c r="I292" s="1"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A293" s="1"/>
+      <c r="A293" s="7"/>
       <c r="B293" s="1"/>
-      <c r="C293" s="1"/>
+      <c r="C293" s="10"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
@@ -6040,9 +6122,9 @@
       <c r="I293" s="1"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A294" s="1"/>
+      <c r="A294" s="7"/>
       <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
+      <c r="C294" s="10"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
@@ -6051,9 +6133,9 @@
       <c r="I294" s="1"/>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="1"/>
+      <c r="A295" s="7"/>
       <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
+      <c r="C295" s="10"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
@@ -6062,9 +6144,9 @@
       <c r="I295" s="1"/>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A296" s="1"/>
+      <c r="A296" s="7"/>
       <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
+      <c r="C296" s="10"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
@@ -6073,9 +6155,9 @@
       <c r="I296" s="1"/>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="1"/>
+      <c r="A297" s="7"/>
       <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
+      <c r="C297" s="10"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
@@ -6084,9 +6166,9 @@
       <c r="I297" s="1"/>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A298" s="1"/>
+      <c r="A298" s="7"/>
       <c r="B298" s="1"/>
-      <c r="C298" s="1"/>
+      <c r="C298" s="10"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
@@ -6095,9 +6177,9 @@
       <c r="I298" s="1"/>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A299" s="1"/>
+      <c r="A299" s="7"/>
       <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
+      <c r="C299" s="10"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
@@ -6106,9 +6188,9 @@
       <c r="I299" s="1"/>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A300" s="1"/>
+      <c r="A300" s="7"/>
       <c r="B300" s="1"/>
-      <c r="C300" s="1"/>
+      <c r="C300" s="10"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
@@ -6117,9 +6199,9 @@
       <c r="I300" s="1"/>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="1"/>
+      <c r="A301" s="7"/>
       <c r="B301" s="1"/>
-      <c r="C301" s="1"/>
+      <c r="C301" s="10"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
@@ -6128,9 +6210,9 @@
       <c r="I301" s="1"/>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A302" s="1"/>
+      <c r="A302" s="7"/>
       <c r="B302" s="1"/>
-      <c r="C302" s="1"/>
+      <c r="C302" s="10"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
@@ -6139,9 +6221,9 @@
       <c r="I302" s="1"/>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="1"/>
+      <c r="A303" s="7"/>
       <c r="B303" s="1"/>
-      <c r="C303" s="1"/>
+      <c r="C303" s="10"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
@@ -6150,9 +6232,9 @@
       <c r="I303" s="1"/>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A304" s="1"/>
+      <c r="A304" s="7"/>
       <c r="B304" s="1"/>
-      <c r="C304" s="1"/>
+      <c r="C304" s="10"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
@@ -6161,9 +6243,9 @@
       <c r="I304" s="1"/>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A305" s="1"/>
+      <c r="A305" s="7"/>
       <c r="B305" s="1"/>
-      <c r="C305" s="1"/>
+      <c r="C305" s="10"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
@@ -6172,9 +6254,9 @@
       <c r="I305" s="1"/>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A306" s="1"/>
+      <c r="A306" s="7"/>
       <c r="B306" s="1"/>
-      <c r="C306" s="1"/>
+      <c r="C306" s="10"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
